--- a/tools/planner-studio/app/seeds/UnitBalance.xlsx
+++ b/tools/planner-studio/app/seeds/UnitBalance.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AttackInterval</t>
+          <t xml:space="preserve">AttackFrequency</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">

--- a/tools/planner-studio/app/seeds/UnitBalance.xlsx
+++ b/tools/planner-studio/app/seeds/UnitBalance.xlsx
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="D22">
         <v>1.32</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="C23">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="D23">
         <v>1.43</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="C24">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="D24">
         <v>1.54</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>800</v>
+        <v>1234</v>
       </c>
       <c r="D25">
         <v>1.65</v>
       </c>
       <c r="E25">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>4</v>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 쿨타임 20% 감소</t>
+          <t xml:space="preserve">공격력 +5%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[자폭드론] 폭발 시 남은 쿨타임 5% 감소</t>
+          <t xml:space="preserve">매 2번째 기본 자폭 피해 +40% (선택지 추가 자폭 제외)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 피해 20% 증가</t>
+          <t xml:space="preserve">일반공격 속도 +5%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[자폭드론] 쿨타임 감소 효과 5% → 10%</t>
+          <t xml:space="preserve">매 2번째 기본 자폭 충전시간 -30% (선택지 추가 자폭 제외)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">치명타 확률/피해 10% 증가.</t>
+          <t xml:space="preserve">유닛 치명타 피해 +50%p</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">

--- a/tools/planner-studio/app/seeds/UnitBalance.xlsx
+++ b/tools/planner-studio/app/seeds/UnitBalance.xlsx
@@ -66,12 +66,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UD_Frog_Mage</t>
+          <t xml:space="preserve">UnitData_Zeltan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog_Mage</t>
+          <t xml:space="preserve">젤탕</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -81,42 +81,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"normal": 1017, "rare": 1024, "epic": 1025, "legend": 1026}</t>
+          <t xml:space="preserve">{"normal": 1004, "rare": 1005, "epic": 1006, "legend": 1007}</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">8708bb1cf4f01c59</t>
         </is>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Mage</t>
+          <t xml:space="preserve">base_UnitData_Zeltan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">growth_UnitData_Zeltan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">bonus_UnitData_Zeltan</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
+          <t xml:space="preserve">UnitData_Deltan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">젤탕</t>
+          <t xml:space="preserve">델탕</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -126,12 +126,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"normal": 1004, "rare": 1005, "epic": 1006, "legend": 1007}</t>
+          <t xml:space="preserve">{"normal": 1000, "rare": 1001, "epic": 1002, "legend": 1003}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708bb1cf4f01c59</t>
+          <t xml:space="preserve">222cf36fcb10c396</t>
         </is>
       </c>
       <c r="F3">
@@ -139,29 +139,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Zeltan</t>
+          <t xml:space="preserve">base_UnitData_Deltan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">growth_UnitData_Zeltan</t>
+          <t xml:space="preserve">growth_UnitData_Deltan</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonus_UnitData_Zeltan</t>
+          <t xml:space="preserve">bonus_UnitData_Deltan</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UD_Frog_Rogue</t>
+          <t xml:space="preserve">UnitData_Betan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog_Rogue</t>
+          <t xml:space="preserve">베탕</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -171,42 +171,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"normal": 1019, "rare": 1030, "epic": 1031, "legend": 1032}</t>
+          <t xml:space="preserve">{"normal": 1012, "rare": 1013, "epic": 1014, "legend": 1015}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">62442b230ddca871</t>
         </is>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Rogue</t>
+          <t xml:space="preserve">base_UnitData_Betan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">growth_UnitData_Betan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">bonus_UnitData_Betan</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
+          <t xml:space="preserve">UnitData_Disigman</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">델탕</t>
+          <t xml:space="preserve">디시그망</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"normal": 1000, "rare": 1001, "epic": 1002, "legend": 1003}</t>
+          <t xml:space="preserve">{"normal": 1100, "rare": 1101, "epic": 1102, "legend": 1103}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">222cf36fcb10c396</t>
+          <t xml:space="preserve">2cb5ef7e94b521a0</t>
         </is>
       </c>
       <c r="F5">
@@ -229,29 +229,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Deltan</t>
+          <t xml:space="preserve">base_UnitData_Disigman</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">growth_UnitData_Deltan</t>
+          <t xml:space="preserve">growth_UnitData_Disigman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonus_UnitData_Deltan</t>
+          <t xml:space="preserve">bonus_UnitData_Disigman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UD_Frog_Archer</t>
+          <t xml:space="preserve">UnitData_Gamman</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog_Archer</t>
+          <t xml:space="preserve">감망</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -261,57 +261,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"normal": 1018, "rare": 1021, "epic": 1022, "legend": 1023}</t>
+          <t xml:space="preserve">{"normal": 1008, "rare": 1009, "epic": 1010, "legend": 1011}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">d3277f41435e2e01</t>
         </is>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Archer</t>
+          <t xml:space="preserve">base_UnitData_Gamman</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">growth_UnitData_Gamman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">bonus_UnitData_Gamman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Betan</t>
+          <t xml:space="preserve">AlphanChief</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">베탕</t>
+          <t xml:space="preserve">알팡</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit</t>
+          <t xml:space="preserve">Chief</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"normal": 1012, "rare": 1013, "epic": 1014, "legend": 1015}</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">62442b230ddca871</t>
+          <t xml:space="preserve">d2c99c2665123dcc</t>
         </is>
       </c>
       <c r="F7">
@@ -319,195 +319,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Betan</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">growth_UnitData_Betan</t>
+          <t xml:space="preserve">growth_AlphanChief</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonus_UnitData_Betan</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UD_Frog_Priest</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frog_Priest</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unit</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"normal": 1020, "rare": 1027, "epic": 1028, "legend": 1029}</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UD_Frog_Priest</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">디시그망</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unit</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"normal": 1100, "rare": 1101, "epic": 1102, "legend": 1103}</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2cb5ef7e94b521a0</t>
-        </is>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">growth_UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonus_UnitData_Disigman</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">감망</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unit</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"normal": 1008, "rare": 1009, "epic": 1010, "legend": 1011}</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">d3277f41435e2e01</t>
-        </is>
-      </c>
-      <c r="F10">
-        <v>20</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">growth_UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonus_UnitData_Gamman</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">알팡</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chief</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">d2c99c2665123dcc</t>
-        </is>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">growth_AlphanChief</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">bonus_AlphanChief</t>
         </is>
@@ -563,7 +383,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Mage</t>
+          <t xml:space="preserve">base_UnitData_Zeltan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -572,16 +392,16 @@
         </is>
       </c>
       <c r="C2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -590,7 +410,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Mage</t>
+          <t xml:space="preserve">base_UnitData_Zeltan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -599,16 +419,16 @@
         </is>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>8</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -617,7 +437,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Mage</t>
+          <t xml:space="preserve">base_UnitData_Zeltan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,16 +446,16 @@
         </is>
       </c>
       <c r="C4">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -644,7 +464,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Mage</t>
+          <t xml:space="preserve">base_UnitData_Zeltan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -653,16 +473,16 @@
         </is>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -671,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Zeltan</t>
+          <t xml:space="preserve">base_UnitData_Deltan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,25 +500,25 @@
         </is>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Zeltan</t>
+          <t xml:space="preserve">base_UnitData_Deltan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -707,25 +527,25 @@
         </is>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Zeltan</t>
+          <t xml:space="preserve">base_UnitData_Deltan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -734,25 +554,25 @@
         </is>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Zeltan</t>
+          <t xml:space="preserve">base_UnitData_Deltan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,25 +581,25 @@
         </is>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Rogue</t>
+          <t xml:space="preserve">base_UnitData_Betan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -788,25 +608,25 @@
         </is>
       </c>
       <c r="C10">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="D10">
+        <v>1.32</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="E10">
-        <v>8</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Rogue</t>
+          <t xml:space="preserve">base_UnitData_Betan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -815,25 +635,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Rogue</t>
+          <t xml:space="preserve">base_UnitData_Betan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -842,25 +662,25 @@
         </is>
       </c>
       <c r="C12">
-        <v>90</v>
+        <v>257</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Rogue</t>
+          <t xml:space="preserve">base_UnitData_Betan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -869,25 +689,25 @@
         </is>
       </c>
       <c r="C13">
-        <v>90</v>
+        <v>1234</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>1.65</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Deltan</t>
+          <t xml:space="preserve">base_UnitData_Disigman</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -896,25 +716,25 @@
         </is>
       </c>
       <c r="C14">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="D14">
-        <v>1.5</v>
+        <v>0.33</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Deltan</t>
+          <t xml:space="preserve">base_UnitData_Disigman</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -923,25 +743,25 @@
         </is>
       </c>
       <c r="C15">
-        <v>160</v>
+        <v>945</v>
       </c>
       <c r="D15">
-        <v>1.6</v>
+        <v>0.33</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Deltan</t>
+          <t xml:space="preserve">base_UnitData_Disigman</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -950,25 +770,25 @@
         </is>
       </c>
       <c r="C16">
-        <v>240</v>
+        <v>2164</v>
       </c>
       <c r="D16">
-        <v>1.7</v>
+        <v>0.33</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UnitData_Deltan</t>
+          <t xml:space="preserve">base_UnitData_Disigman</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -977,25 +797,25 @@
         </is>
       </c>
       <c r="C17">
-        <v>800</v>
+        <v>14545</v>
       </c>
       <c r="D17">
-        <v>1.8</v>
+        <v>0.33</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Archer</t>
+          <t xml:space="preserve">base_UnitData_Gamman</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1004,25 +824,25 @@
         </is>
       </c>
       <c r="C18">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D18">
+        <v>0.9</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18">
         <v>1</v>
       </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Archer</t>
+          <t xml:space="preserve">base_UnitData_Gamman</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1031,25 +851,25 @@
         </is>
       </c>
       <c r="C19">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Archer</t>
+          <t xml:space="preserve">base_UnitData_Gamman</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1058,25 +878,25 @@
         </is>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="D20">
+        <v>1.1</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
         <v>1</v>
-      </c>
-      <c r="E20">
-        <v>8</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_UD_Frog_Archer</t>
+          <t xml:space="preserve">base_UnitData_Gamman</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1085,450 +905,18 @@
         </is>
       </c>
       <c r="C21">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">normal</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>136</v>
-      </c>
-      <c r="D22">
-        <v>1.32</v>
-      </c>
-      <c r="E22">
-        <v>6</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rare</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>197</v>
-      </c>
-      <c r="D23">
-        <v>1.43</v>
-      </c>
-      <c r="E23">
-        <v>6</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">epic</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>257</v>
-      </c>
-      <c r="D24">
-        <v>1.54</v>
-      </c>
-      <c r="E24">
-        <v>6</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legend</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>1234</v>
-      </c>
-      <c r="D25">
-        <v>1.65</v>
-      </c>
-      <c r="E25">
-        <v>6</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UD_Frog_Priest</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">normal</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>70</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>12</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UD_Frog_Priest</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rare</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>70</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>12</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UD_Frog_Priest</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">epic</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>70</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>12</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UD_Frog_Priest</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legend</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>70</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>12</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">normal</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>291</v>
-      </c>
-      <c r="D30">
-        <v>0.33</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rare</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>945</v>
-      </c>
-      <c r="D31">
-        <v>0.33</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>2</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">epic</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>2164</v>
-      </c>
-      <c r="D32">
-        <v>0.33</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>3</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legend</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>14545</v>
-      </c>
-      <c r="D33">
-        <v>0.33</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>4</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">normal</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>80</v>
-      </c>
-      <c r="D34">
-        <v>0.9</v>
-      </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rare</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>160</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>6</v>
-      </c>
-      <c r="F35">
-        <v>2</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">epic</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>240</v>
-      </c>
-      <c r="D36">
-        <v>1.1</v>
-      </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
-      <c r="F36">
-        <v>3</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">base_UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">legend</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>800</v>
-      </c>
-      <c r="D37">
-        <v>1.2</v>
-      </c>
-      <c r="E37">
-        <v>6</v>
-      </c>
-      <c r="F37">
-        <v>4</v>
-      </c>
-      <c r="G37">
         <v>1</v>
       </c>
     </row>
@@ -4436,7 +3824,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">유닛 치명타 피해 +50%p</t>
+          <t xml:space="preserve">유닛 치명타 피해 +50%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">

--- a/tools/planner-studio/app/seeds/UnitBalance.xlsx
+++ b/tools/planner-studio/app/seeds/UnitBalance.xlsx
@@ -6,6 +6,8 @@
     <sheet name="BaseStats" sheetId="2" r:id="rId2"/>
     <sheet name="UpgradeStats" sheetId="3" r:id="rId3"/>
     <sheet name="LevelBonuses" sheetId="4" r:id="rId4"/>
+    <sheet name="BonusEffect" sheetId="5" r:id="rId5"/>
+    <sheet name="BonusDescription" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -3404,22 +3406,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">식량 생산 쿨타임 10% 감소</t>
+          <t xml:space="preserve">자체 식량 생산속도 +10%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodSpeed","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3434,22 +3436,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">등장 시 식량 즉시 2회 생산</t>
+          <t xml:space="preserve">보스 처치 시 자체 식량 5초분 지급</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BossFoodSeconds","ValueMode":"Flat","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3464,22 +3466,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">보스 처치 시 식량 즉시 3회 생산</t>
+          <t xml:space="preserve">자체 식량 생산량 +15%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodProduction","ValueMode":"Percent","Value":15,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3494,22 +3496,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25% 확률로 식량 2배 생산</t>
+          <t xml:space="preserve">매 5번째 자체 식량 생산량 2배</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodFifthMultiplier","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3524,22 +3526,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">자체 식량 생산량 20% 증가</t>
+          <t xml:space="preserve">매 5번째 자체 식량 생산량 2.5배로 교체</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodFifthMultiplier","ValueMode":"Flat","Value":2.5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3554,22 +3556,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[해킹] 최대 스택 +5</t>
+          <t xml:space="preserve">공격속도 +10%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicAttackFrequency","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3584,22 +3586,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 사용 시 20% 확률로 [해킹] +1</t>
+          <t xml:space="preserve">스킬 충전 필요 공격 횟수 -1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChargeAttackReduction","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3614,22 +3616,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 충전 공격 횟수 -1</t>
+          <t xml:space="preserve">공유 [해킹] 최대 스택 +10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingCapacity","ValueMode":"Flat","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3644,22 +3646,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 사용 시 [해킹] 추가 부여 확정</t>
+          <t xml:space="preserve">스킬 사용 시 [해킹] 추가 생산: 노말 1 / 레어 1 / 에픽 2 / 전설 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingProducedNormal","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingProducedRare","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingProducedEpic","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingProducedLegend","ValueMode":"Flat","Value":3,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3674,22 +3676,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[해킹] 최대 스택 추가 +10</t>
+          <t xml:space="preserve">[해킹] 스킬 사용 후 2초간 자신의 공격속도 +15% (재발동 시 시간 갱신)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingPostSpeed","ValueMode":"Percent","Value":15,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingPostDuration","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3709,17 +3711,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"Attack","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3734,22 +3736,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">매 2번째 기본 자폭 피해 +40% (선택지 추가 자폭 제외)</t>
+          <t xml:space="preserve">매 2번째 기본 [자폭드론] 피해 +40% (선택지 추가 자폭 제외)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"EveryNthCycleBonus","Stat":"Attack","ValueMode":"Percent","Value":0,"CycleId":"basic_skill","Every":2,"DamageBonusPercent":40,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3769,17 +3771,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicAttackFrequency","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3794,22 +3796,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">매 2번째 기본 자폭 충전시간 -30% (선택지 추가 자폭 제외)</t>
+          <t xml:space="preserve">매 2번째 기본 [자폭드론] 충전시간 -30% (선택지 추가 자폭 제외)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"EveryNthCycleBonus","Stat":"Attack","ValueMode":"Percent","Value":0,"CycleId":"basic_skill","Every":2,"DamageBonusPercent":0,"ChargeReductionPercent":30}]}</t>
         </is>
       </c>
     </row>
@@ -3824,22 +3826,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">유닛 치명타 피해 +50%</t>
+          <t xml:space="preserve">일반공격·자폭 치명타 피해 +50%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"CriticalDamage","ValueMode":"PercentagePoints","Value":50,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3854,22 +3856,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격력 10% 증가</t>
+          <t xml:space="preserve">공격력 +5%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"Attack","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3884,22 +3886,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 충전 공격 횟수 -1</t>
+          <t xml:space="preserve">시간 회복 후 다음 정규 일반공격 피해 +30% (1회 저장, 중첩 없음)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"RecoveryNextBasic","ValueMode":"Percent","Value":30,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3914,22 +3916,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격속도 10% 증가</t>
+          <t xml:space="preserve">공격속도 +5%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicAttackFrequency","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3944,22 +3946,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">일반공격 시 25% 확률로 추가 공격</t>
+          <t xml:space="preserve">시간 회복량 +10%</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"TimeRecovery","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -3974,22 +3976,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">일반공격 피해 20% 증가</t>
+          <t xml:space="preserve">일반공격 피해 +15%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicDamage","ValueMode":"Percent","Value":15,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4004,22 +4006,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격력 10% 증가</t>
+          <t xml:space="preserve">공격력 +10%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"Attack","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4034,22 +4036,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 쿨타임 20% 감소</t>
+          <t xml:space="preserve">[해킹] 스택 부분 피해 +20%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingStackDamage","ValueMode":"Percent","Value":20,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4064,22 +4066,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 피해 20% 증가</t>
+          <t xml:space="preserve">스킬 쿨타임 -10%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"SkillCooldownReduction","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4094,22 +4096,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 사용 시 [해킹] 추가 소모 +1</t>
+          <t xml:space="preserve">[해킹] 추가 소모 한도: 노말 1 / 레어 1 / 에픽 2 / 전설 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingConsumedNormal","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingConsumedRare","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingConsumedEpic","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingConsumedLegend","ValueMode":"Flat","Value":4,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4124,22 +4126,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">치명타 확률/피해 10% 증가.</t>
+          <t xml:space="preserve">치명타 확률 +10%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"CriticalChance","ValueMode":"PercentagePoints","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4154,22 +4156,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">[액티브 스킬] 쿨타임 10% 감소</t>
+          <t xml:space="preserve">[액티브 스킬] 쿨타임 -10%</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefCooldown","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4184,22 +4186,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">패턴 무효화 시 남은 쿨타임 15% 감소</t>
+          <t xml:space="preserve">전투 시작 시 [액티브 스킬] 1회 충전 완료</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefStartsReady","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4214,22 +4216,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">전체 유닛 공격력 5% 증가</t>
+          <t xml:space="preserve">전체 유닛 공격력 +5% (족장 고정 집결 피해·식량 제외)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefGlobalAttack","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4244,22 +4246,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[액티브 스킬] 사용 시 전체 유닛 공격속도 증가</t>
+          <t xml:space="preserve">[액티브 스킬] 사용 시 10초간 전체 유닛 {공격속도효과} +20% (시간 갱신)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CompositeBonus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefSpeed","ValueMode":"Percent","Value":20,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"ChiefSpeedDuration","ValueMode":"Flat","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4274,22 +4276,2666 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">전체 유닛 스킬 쿨타임 10% 감소</t>
+          <t xml:space="preserve">집결 적중 시 5초간 보스가 받는 피해 +10%</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DescriptionOnly</t>
+          <t xml:space="preserve">Defined</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t xml:space="preserve">CompositeBonus</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefDamageTaken","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"ChiefDamageTakenDuration","ValueMode":"Flat","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PartIndex</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stat</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ValueMode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CycleId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DamageBonusPercent</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChargeReductionPercent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EveryNthCycleBonus</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basic_skill</t>
+        </is>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackFrequency</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EveryNthCycleBonus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basic_skill</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalDamage</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PercentagePoints</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackFrequency</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChargeAttackReduction</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingCapacity</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingProducedNormal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingProducedRare</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingProducedEpic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingProducedLegend</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingPostSpeed</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>15</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingPostDuration</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingStackDamage</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillCooldownReduction</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingConsumedNormal</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingConsumedRare</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingConsumedEpic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingConsumedLegend</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalChance</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PercentagePoints</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RecoveryNextBasic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>30</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackFrequency</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TimeRecovery</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicDamage</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>15</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodSpeed</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BossFoodSeconds</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodProduction</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>12</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodFifthMultiplier</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodFifthMultiplier</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>2.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefCooldown</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefStartsReady</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefGlobalAttack</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefSpeed</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>12</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefSpeedDuration</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefDamageTaken</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefDamageTakenDuration</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HighlightNumbers</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LinkTerms</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EffectLink</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공격력 +5%</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매 2번째 기본 [자폭드론] 피해 +40% (선택지 추가 자폭 제외)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일반공격 속도 +5%</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매 2번째 기본 [자폭드론] 충전시간 -30% (선택지 추가 자폭 제외)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Betan</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일반공격·자폭 치명타 피해 +50%</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공격속도 +10%</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스킬 충전 필요 공격 횟수 -1</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공유 [해킹] 최대 스택 +10</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스킬 사용 시 [해킹] 추가 생산: 노말 1 / 레어 1 / 에픽 2 / 전설 3</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Deltan</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[해킹] 스킬 사용 후 2초간 자신의 공격속도 +15% (재발동 시 시간 갱신)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공격력 +10%</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[해킹] 스택 부분 피해 +20%</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스킬 쿨타임 -10%</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[해킹] 추가 소모 한도: 노말 1 / 레어 1 / 에픽 2 / 전설 4</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치명타 확률 +10%</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공격력 +5%</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간 회복 후 다음 정규 일반공격 피해 +30% (1회 저장, 중첩 없음)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공격속도 +5%</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간 회복량 +10%</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일반공격 피해 +15%</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자체 식량 생산속도 +10%</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보스 처치 시 자체 식량 5초분 지급</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자체 식량 생산량 +15%</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매 5번째 자체 식량 생산량 2배</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매 5번째 자체 식량 생산량 2.5배로 교체</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[액티브 스킬] 쿨타임 -10%</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전투 시작 시 [액티브 스킬] 1회 충전 완료</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 유닛 공격력 +5% (족장 고정 집결 피해·식량 제외)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>12</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[액티브 스킬] 사용 시 10초간 전체 유닛 {공격속도효과} +20% (시간 갱신)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefAttackSpeed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집결 적중 시 5초간 보스가 받는 피해 +10%</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
     </row>

--- a/tools/planner-studio/app/seeds/UnitBalance.xlsx
+++ b/tools/planner-studio/app/seeds/UnitBalance.xlsx
@@ -6,8 +6,8 @@
     <sheet name="BaseStats" sheetId="2" r:id="rId2"/>
     <sheet name="UpgradeStats" sheetId="3" r:id="rId3"/>
     <sheet name="LevelBonuses" sheetId="4" r:id="rId4"/>
-    <sheet name="BonusEffect" sheetId="5" r:id="rId5"/>
-    <sheet name="BonusDescription" sheetId="6" r:id="rId6"/>
+    <sheet name="BonusDefinition" sheetId="5" r:id="rId5"/>
+    <sheet name="BonusEffect" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -3379,21 +3379,6 @@
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectStatus</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectKey</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EffectParams</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3409,21 +3394,6 @@
           <t xml:space="preserve">자체 식량 생산속도 +10%</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodSpeed","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3439,21 +3409,6 @@
           <t xml:space="preserve">보스 처치 시 자체 식량 5초분 지급</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BossFoodSeconds","ValueMode":"Flat","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3469,21 +3424,6 @@
           <t xml:space="preserve">자체 식량 생산량 +15%</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodProduction","ValueMode":"Percent","Value":15,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3499,21 +3439,6 @@
           <t xml:space="preserve">매 5번째 자체 식량 생산량 2배</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodFifthMultiplier","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3529,21 +3454,6 @@
           <t xml:space="preserve">매 5번째 자체 식량 생산량 2.5배로 교체</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"FoodFifthMultiplier","ValueMode":"Flat","Value":2.5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3559,21 +3469,6 @@
           <t xml:space="preserve">공격속도 +10%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicAttackFrequency","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3589,21 +3484,6 @@
           <t xml:space="preserve">스킬 충전 필요 공격 횟수 -1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChargeAttackReduction","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3619,21 +3499,6 @@
           <t xml:space="preserve">공유 [해킹] 최대 스택 +10</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingCapacity","ValueMode":"Flat","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3649,21 +3514,6 @@
           <t xml:space="preserve">스킬 사용 시 [해킹] 추가 생산: 노말 1 / 레어 1 / 에픽 2 / 전설 3</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingProducedNormal","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingProducedRare","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingProducedEpic","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingProducedLegend","ValueMode":"Flat","Value":3,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3679,21 +3529,6 @@
           <t xml:space="preserve">[해킹] 스킬 사용 후 2초간 자신의 공격속도 +15% (재발동 시 시간 갱신)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingPostSpeed","ValueMode":"Percent","Value":15,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingPostDuration","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3709,21 +3544,6 @@
           <t xml:space="preserve">공격력 +5%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"Attack","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3739,21 +3559,6 @@
           <t xml:space="preserve">매 2번째 기본 [자폭드론] 피해 +40% (선택지 추가 자폭 제외)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"EveryNthCycleBonus","Stat":"Attack","ValueMode":"Percent","Value":0,"CycleId":"basic_skill","Every":2,"DamageBonusPercent":40,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3769,21 +3574,6 @@
           <t xml:space="preserve">일반공격 속도 +5%</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicAttackFrequency","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3799,21 +3589,6 @@
           <t xml:space="preserve">매 2번째 기본 [자폭드론] 충전시간 -30% (선택지 추가 자폭 제외)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"EveryNthCycleBonus","Stat":"Attack","ValueMode":"Percent","Value":0,"CycleId":"basic_skill","Every":2,"DamageBonusPercent":0,"ChargeReductionPercent":30}]}</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3829,21 +3604,6 @@
           <t xml:space="preserve">일반공격·자폭 치명타 피해 +50%</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"CriticalDamage","ValueMode":"PercentagePoints","Value":50,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3859,21 +3619,6 @@
           <t xml:space="preserve">공격력 +5%</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"Attack","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3889,21 +3634,6 @@
           <t xml:space="preserve">시간 회복 후 다음 정규 일반공격 피해 +30% (1회 저장, 중첩 없음)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"RecoveryNextBasic","ValueMode":"Percent","Value":30,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3919,21 +3649,6 @@
           <t xml:space="preserve">공격속도 +5%</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicAttackFrequency","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3949,21 +3664,6 @@
           <t xml:space="preserve">시간 회복량 +10%</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"TimeRecovery","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3979,21 +3679,6 @@
           <t xml:space="preserve">일반공격 피해 +15%</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"BasicDamage","ValueMode":"Percent","Value":15,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4009,21 +3694,6 @@
           <t xml:space="preserve">공격력 +10%</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"Attack","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4039,21 +3709,6 @@
           <t xml:space="preserve">[해킹] 스택 부분 피해 +20%</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingStackDamage","ValueMode":"Percent","Value":20,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4069,21 +3724,6 @@
           <t xml:space="preserve">스킬 쿨타임 -10%</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"SkillCooldownReduction","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4099,21 +3739,6 @@
           <t xml:space="preserve">[해킹] 추가 소모 한도: 노말 1 / 레어 1 / 에픽 2 / 전설 4</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"HackingConsumedNormal","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingConsumedRare","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingConsumedEpic","ValueMode":"Flat","Value":2,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"HackingConsumedLegend","ValueMode":"Flat","Value":4,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4129,21 +3754,6 @@
           <t xml:space="preserve">치명타 확률 +10%</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"CriticalChance","ValueMode":"PercentagePoints","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4159,21 +3769,6 @@
           <t xml:space="preserve">[액티브 스킬] 쿨타임 -10%</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefCooldown","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4189,21 +3784,6 @@
           <t xml:space="preserve">전투 시작 시 [액티브 스킬] 1회 충전 완료</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefStartsReady","ValueMode":"Flat","Value":1,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4219,21 +3799,6 @@
           <t xml:space="preserve">전체 유닛 공격력 +5% (족장 고정 집결 피해·식량 제외)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefGlobalAttack","ValueMode":"Percent","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4249,21 +3814,6 @@
           <t xml:space="preserve">[액티브 스킬] 사용 시 10초간 전체 유닛 {공격속도효과} +20% (시간 갱신)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefSpeed","ValueMode":"Percent","Value":20,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"ChiefSpeedDuration","ValueMode":"Flat","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4277,21 +3827,6 @@
       <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">집결 적중 시 5초간 보스가 받는 피해 +10%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Defined</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CompositeBonus</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"Parts":[{"EffectType":"StatModifierBonus","Stat":"ChiefDamageTaken","ValueMode":"Percent","Value":10,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0},{"EffectType":"StatModifierBonus","Stat":"ChiefDamageTakenDuration","ValueMode":"Flat","Value":5,"CycleId":"","Every":0,"DamageBonusPercent":0,"ChargeReductionPercent":0}]}</t>
         </is>
       </c>
     </row>
@@ -4302,1819 +3837,980 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="4" width="28" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="72" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">BonusId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitKey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Level</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PartIndex</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">EffectType</t>
+          <t xml:space="preserve">DescriptionTemplate</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stat</t>
+          <t xml:space="preserve">HighlightNumbers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ValueMode</t>
+          <t xml:space="preserve">LinkTerms</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CycleId</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DamageBonusPercent</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChargeReductionPercent</t>
+          <t xml:space="preserve">EffectLink</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">betan_lv3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Betan</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
+          <t xml:space="preserve">공격력 +{attack.Value}%</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t xml:space="preserve">betan_lv6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Betan</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EveryNthCycleBonus</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">basic_skill</t>
-        </is>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
+          <t xml:space="preserve">매 {cycle.Every}번째 기본 [자폭드론] 피해 +{cycle.DamageBonusPercent}% (선택지 추가 자폭 제외)</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">betan_lv9</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Betan</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>9</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BasicAttackFrequency</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
+          <t xml:space="preserve">일반공격 속도 +{basicAttackFrequency.Value}%</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">betan_lv12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Betan</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EveryNthCycleBonus</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">basic_skill</t>
-        </is>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>30</v>
+          <t xml:space="preserve">매 {cycle.Every}번째 기본 [자폭드론] 충전시간 -{cycle.ChargeReductionPercent}% (선택지 추가 자폭 제외)</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t xml:space="preserve">betan_lv15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Betan</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>15</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CriticalDamage</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PercentagePoints</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
+          <t xml:space="preserve">일반공격·자폭 치명타 피해 +{criticalDamage.Value}%</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">deltan_lv3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Deltan</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BasicAttackFrequency</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
+          <t xml:space="preserve">공격속도 +{basicAttackFrequency.Value}%</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">deltan_lv6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Deltan</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>6</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChargeAttackReduction</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
+          <t xml:space="preserve">스킬 충전 필요 공격 횟수 -{chargeAttackReduction.Value}</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">deltan_lv9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Deltan</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingCapacity</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
+          <t xml:space="preserve">공유 [해킹] 최대 스택 +{hackingCapacity.Value}</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t xml:space="preserve">deltan_lv12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Deltan</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>12</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingProducedNormal</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
+          <t xml:space="preserve">스킬 사용 시 [해킹] 추가 생산: 노말 {hackingProducedNormal.Normal} / 레어 {hackingProducedNormal.Rare} / 에픽 {hackingProducedNormal.Epic} / 전설 {hackingProducedNormal.Legend}</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">deltan_lv15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Deltan</t>
         </is>
       </c>
-      <c r="B11">
-        <v>12</v>
-      </c>
       <c r="C11">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingProducedRare</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
+          <t xml:space="preserve">[해킹] 스킬 사용 후 {hackingPostSpeed.Duration}초간 자신의 공격속도 +{hackingPostSpeed.Value}% (재발동 시 시간 갱신)</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>12</v>
+          <t xml:space="preserve">gamman_lv3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingProducedEpic</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
+          <t xml:space="preserve">공격력 +{attack.Value}%</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>12</v>
+          <t xml:space="preserve">gamman_lv6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingProducedLegend</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
+          <t xml:space="preserve">[해킹] 스택 부분 피해 +{hackingStackDamage.Value}%</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>15</v>
+          <t xml:space="preserve">gamman_lv9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingPostSpeed</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>15</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
+          <t xml:space="preserve">스킬 쿨타임 -{skillCooldownReduction.Value}%</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>15</v>
+          <t xml:space="preserve">gamman_lv12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Gamman</t>
+        </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingPostDuration</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
+          <t xml:space="preserve">[해킹] 추가 소모 한도: 노말 {hackingConsumedNormal.Normal} / 레어 {hackingConsumedNormal.Rare} / 에픽 {hackingConsumedNormal.Epic} / 전설 {hackingConsumedNormal.Legend}</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t xml:space="preserve">gamman_lv15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t xml:space="preserve">UnitData_Gamman</t>
         </is>
       </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
       <c r="C16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>10</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
+          <t xml:space="preserve">치명타 확률 +{criticalChance.Value}%</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>6</v>
+          <t xml:space="preserve">disigman_lv3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingStackDamage</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>20</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
+          <t xml:space="preserve">공격력 +{attack.Value}%</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>9</v>
+          <t xml:space="preserve">disigman_lv6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SkillCooldownReduction</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
+          <t xml:space="preserve">시간 회복 후 다음 정규 일반공격 피해 +{recoveryNextBasic.Value}% (1회 저장, 중첩 없음)</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>12</v>
+          <t xml:space="preserve">disigman_lv9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingConsumedNormal</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
+          <t xml:space="preserve">공격속도 +{basicAttackFrequency.Value}%</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t xml:space="preserve">disigman_lv12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
+      </c>
+      <c r="C20">
         <v>12</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingConsumedRare</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
+          <t xml:space="preserve">시간 회복량 +{timeRecovery.Value}%</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>12</v>
+          <t xml:space="preserve">disigman_lv15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Disigman</t>
+        </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingConsumedEpic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
+          <t xml:space="preserve">일반공격 피해 +{basicDamage.Value}%</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>12</v>
+          <t xml:space="preserve">zeltan_lv3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HackingConsumedLegend</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>4</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
+          <t xml:space="preserve">자체 식량 생산속도 +{foodSpeed.Value}%</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>15</v>
+          <t xml:space="preserve">zeltan_lv6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CriticalChance</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PercentagePoints</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>10</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
+          <t xml:space="preserve">보스 처치 시 자체 식량 {bossFoodSeconds.Value}초분 지급</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>3</v>
+          <t xml:space="preserve">zeltan_lv9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attack</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
+          <t xml:space="preserve">자체 식량 생산량 +{foodProduction.Value}%</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>6</v>
+          <t xml:space="preserve">zeltan_lv12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RecoveryNextBasic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>30</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
+          <t xml:space="preserve">매 5번째 자체 식량 생산량 {foodFifthMultiplier.Value}배</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>9</v>
+          <t xml:space="preserve">zeltan_lv15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UnitData_Zeltan</t>
+        </is>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BasicAttackFrequency</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
+          <t xml:space="preserve">매 5번째 자체 식량 생산량 {foodFifthMultiplier.Value}배로 교체</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>12</v>
+          <t xml:space="preserve">alphan_lv3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TimeRecovery</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>10</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
+          <t xml:space="preserve">[액티브 스킬] 쿨타임 -{chiefCooldown.Value}%</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>15</v>
+          <t xml:space="preserve">alphan_lv6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BasicDamage</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>15</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
+          <t xml:space="preserve">전투 시작 시 [액티브 스킬] {chiefStartsReady.Value}회 충전 완료</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>3</v>
+          <t xml:space="preserve">alphan_lv9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FoodSpeed</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>10</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
+          <t xml:space="preserve">전체 유닛 공격력 +{chiefGlobalAttack.Value}% (족장 고정 집결 피해·식량 제외)</t>
+        </is>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>6</v>
+          <t xml:space="preserve">alphan_lv12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BossFoodSeconds</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>5</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
+          <t xml:space="preserve">[액티브 스킬] 사용 시 {chiefSpeed.Duration}초간 전체 유닛 {공격속도효과} +{chiefSpeed.Value}% (시간 갱신)</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefAttackSpeed</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>9</v>
+          <t xml:space="preserve">alphan_lv15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AlphanChief</t>
+        </is>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FoodProduction</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>15</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>12</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FoodFifthMultiplier</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>15</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FoodFifthMultiplier</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>2.5</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>3</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefCooldown</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>6</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefStartsReady</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>9</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefGlobalAttack</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>5</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>12</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefSpeed</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>20</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>12</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefSpeedDuration</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>10</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>15</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefDamageTaken</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Percent</t>
-        </is>
-      </c>
-      <c r="G39">
-        <v>10</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>15</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StatModifierBonus</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChiefDamageTakenDuration</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flat</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>5</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
+          <t xml:space="preserve">집결 적중 시 {chiefDamageTaken.Duration}초간 보스가 받는 피해 +{chiefDamageTaken.Value}%</t>
+        </is>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6124,818 +4820,1003 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="4" width="28" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitKey</t>
+          <t xml:space="preserve">BonusId</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level</t>
+          <t xml:space="preserve">EffectKey</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Description</t>
+          <t xml:space="preserve">EffectType</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HighlightNumbers</t>
+          <t xml:space="preserve">Stat</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LinkTerms</t>
+          <t xml:space="preserve">ValueMode</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">EffectLink</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>3</v>
+          <t xml:space="preserve">betan_lv3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attack</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격력 +5%</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>6</v>
+          <t xml:space="preserve">betan_lv6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cycle</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">매 2번째 기본 [자폭드론] 피해 +40% (선택지 추가 자폭 제외)</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+          <t xml:space="preserve">EveryNthCycleBonus</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">2,40,0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>9</v>
+          <t xml:space="preserve">betan_lv9</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basicAttackFrequency</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">일반공격 속도 +5%</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackFrequency</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>12</v>
+          <t xml:space="preserve">betan_lv12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cycle</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">매 2번째 기본 [자폭드론] 충전시간 -30% (선택지 추가 자폭 제외)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+          <t xml:space="preserve">EveryNthCycleBonus</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">2,0,30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Betan</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>15</v>
+          <t xml:space="preserve">betan_lv15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criticalDamage</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">일반공격·자폭 치명타 피해 +50%</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalDamage</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PercentagePoints</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>3</v>
+          <t xml:space="preserve">deltan_lv3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basicAttackFrequency</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격속도 +10%</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackFrequency</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>6</v>
+          <t xml:space="preserve">deltan_lv6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chargeAttackReduction</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 충전 필요 공격 횟수 -1</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChargeAttackReduction</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>9</v>
+          <t xml:space="preserve">deltan_lv9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hackingCapacity</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">공유 [해킹] 최대 스택 +10</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingCapacity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>12</v>
+          <t xml:space="preserve">deltan_lv12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hackingProducedNormal</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 사용 시 [해킹] 추가 생산: 노말 1 / 레어 1 / 에픽 2 / 전설 3</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
+          <t xml:space="preserve">HackingProductionBonus</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">1,1,2,3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Deltan</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>15</v>
+          <t xml:space="preserve">deltan_lv15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hackingPostSpeed</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[해킹] 스킬 사용 후 2초간 자신의 공격속도 +15% (재발동 시 시간 갱신)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+          <t xml:space="preserve">HackingAttackSpeedBonus</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">15,2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>3</v>
+          <t xml:space="preserve">gamman_lv3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attack</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격력 +10%</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>6</v>
+          <t xml:space="preserve">gamman_lv6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hackingStackDamage</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[해킹] 스택 부분 피해 +20%</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HackingStackDamage</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>9</v>
+          <t xml:space="preserve">gamman_lv9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skillCooldownReduction</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">스킬 쿨타임 -10%</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SkillCooldownReduction</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>12</v>
+          <t xml:space="preserve">gamman_lv12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hackingConsumedNormal</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[해킹] 추가 소모 한도: 노말 1 / 레어 1 / 에픽 2 / 전설 4</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
+          <t xml:space="preserve">HackingConsumptionBonus</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">1,1,2,4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Gamman</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>15</v>
+          <t xml:space="preserve">gamman_lv15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criticalChance</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">치명타 확률 +10%</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CriticalChance</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PercentagePoints</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>3</v>
+          <t xml:space="preserve">disigman_lv3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attack</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격력 +5%</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attack</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>6</v>
+          <t xml:space="preserve">disigman_lv6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recoveryNextBasic</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">시간 회복 후 다음 정규 일반공격 피해 +30% (1회 저장, 중첩 없음)</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RecoveryNextBasic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>9</v>
+          <t xml:space="preserve">disigman_lv9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basicAttackFrequency</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격속도 +5%</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicAttackFrequency</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>12</v>
+          <t xml:space="preserve">disigman_lv12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timeRecovery</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">시간 회복량 +10%</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TimeRecovery</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Disigman</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>15</v>
+          <t xml:space="preserve">disigman_lv15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">basicDamage</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">일반공격 피해 +15%</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BasicDamage</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>3</v>
+          <t xml:space="preserve">zeltan_lv3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foodSpeed</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">자체 식량 생산속도 +10%</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodSpeed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>6</v>
+          <t xml:space="preserve">zeltan_lv6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bossFoodSeconds</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">보스 처치 시 자체 식량 5초분 지급</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BossFoodSeconds</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>9</v>
+          <t xml:space="preserve">zeltan_lv9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foodProduction</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">자체 식량 생산량 +15%</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodProduction</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>12</v>
+          <t xml:space="preserve">zeltan_lv12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foodFifthMultiplier</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">매 5번째 자체 식량 생산량 2배</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodFifthMultiplier</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">UnitData_Zeltan</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>15</v>
+          <t xml:space="preserve">zeltan_lv15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foodFifthMultiplier</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">매 5번째 자체 식량 생산량 2.5배로 교체</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FoodFifthMultiplier</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">2.5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>3</v>
+          <t xml:space="preserve">alphan_lv3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiefCooldown</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">[액티브 스킬] 쿨타임 -10%</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefCooldown</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>6</v>
+          <t xml:space="preserve">alphan_lv6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiefStartsReady</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 시작 시 [액티브 스킬] 1회 충전 완료</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefStartsReady</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flat</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>9</v>
+          <t xml:space="preserve">alphan_lv9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiefGlobalAttack</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">전체 유닛 공격력 +5% (족장 고정 집결 피해·식량 제외)</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
+          <t xml:space="preserve">StatModifierBonus</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChiefGlobalAttack</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Percent</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>12</v>
+          <t xml:space="preserve">alphan_lv12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiefSpeed</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[액티브 스킬] 사용 시 10초간 전체 유닛 {공격속도효과} +20% (시간 갱신)</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
+          <t xml:space="preserve">ChiefAttackSpeedBonus</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChiefAttackSpeed</t>
+          <t xml:space="preserve">20,10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AlphanChief</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>15</v>
+          <t xml:space="preserve">alphan_lv15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiefDamageTaken</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">집결 적중 시 5초간 보스가 받는 피해 +10%</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
+          <t xml:space="preserve">RallyVulnerabilityBonus</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">10,5</t>
         </is>
       </c>
     </row>

--- a/tools/planner-studio/app/seeds/UnitBalance.xlsx
+++ b/tools/planner-studio/app/seeds/UnitBalance.xlsx
@@ -430,7 +430,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -457,7 +457,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>0</v>
